--- a/src/Features/Integration/data/2025_sem2/zi/master.xlsx
+++ b/src/Features/Integration/data/2025_sem2/zi/master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding\ScheduleLib\src\Features\Integration\data\2025_sem2\zi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{67BE1B5A-D98E-469E-B4C6-5F47EFDD6053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BABBEB1-2268-4CF1-B722-0BBCDAC6A4CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{ACC1EEF4-C53F-4624-81D6-BBDA19208C63}"/>
+    <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{ACC1EEF4-C53F-4624-81D6-BBDA19208C63}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -144,19 +144,19 @@
     <t>Securitatea tranzacțiilor electronice (lab), O. Cerbu, 145a/4</t>
   </si>
   <si>
-    <t>par: Cloud computing pentru știința datelor (lab, sb1), A. Prepeliță, 219/4a 
-Procesarea limbajului natural (lab, sb 2), T. Bumbu, 218/4a</t>
-  </si>
-  <si>
-    <t>imp: Cloud computing pentru știința datelor (lab, sb2), A. Prepeliță, 219/4a 
-Procesarea limbajului natural (lab, sb 1), T. Bumbu, 218/4a</t>
-  </si>
-  <si>
     <t>III
 11:30-13:00</t>
   </si>
   <si>
     <t>Învățare profundă (lab, sb1 par, sb 2 imp), T. Bumbu, 218/4a</t>
+  </si>
+  <si>
+    <t>Cloud computing pentru știința datelor (lab, sb1, par), A. Prepeliță, 219/4a 
+Procesarea limbajului natural (lab, sb 2), T. Bumbu, 218/4a</t>
+  </si>
+  <si>
+    <t>Cloud computing pentru știința datelor (lab, sb2, imp), A. Prepeliță, 219/4a 
+Procesarea limbajului natural (lab, sb 1), T. Bumbu, 218/4a</t>
   </si>
 </sst>
 </file>
@@ -347,6 +347,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -363,21 +378,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -695,27 +695,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F9CB3DD-4EB8-464D-96C3-98812BDDE9D7}">
   <dimension ref="B1:E18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.453125" customWidth="1"/>
-    <col min="3" max="3" width="17.6328125" customWidth="1"/>
-    <col min="4" max="5" width="38.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="5" width="38.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:5" ht="20.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="5" t="s">
+    <row r="1" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:5" ht="21" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="9" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="10"/>
-    </row>
-    <row r="3" spans="2:5" ht="20.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
+      <c r="E2" s="15"/>
+    </row>
+    <row r="3" spans="2:5" ht="21" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="12"/>
+      <c r="C3" s="13"/>
       <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
@@ -723,8 +723,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="11" t="s">
+    <row r="4" spans="2:5" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -733,16 +733,16 @@
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="2:5" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="12"/>
+    <row r="5" spans="2:5" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="6"/>
       <c r="C5" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="2:5" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="11" t="s">
+    <row r="6" spans="2:5" ht="63.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -753,8 +753,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="13"/>
+    <row r="7" spans="2:5" ht="63.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="7"/>
       <c r="C7" s="4" t="s">
         <v>5</v>
       </c>
@@ -765,8 +765,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12"/>
+    <row r="8" spans="2:5" ht="63.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="6"/>
       <c r="C8" s="4" t="s">
         <v>6</v>
       </c>
@@ -777,8 +777,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="41.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B9" s="11" t="s">
+    <row r="9" spans="2:5" ht="42.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B9" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -789,8 +789,8 @@
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="2:5" ht="41.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B10" s="12"/>
+    <row r="10" spans="2:5" ht="42.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="6"/>
       <c r="C10" s="3" t="s">
         <v>6</v>
       </c>
@@ -799,8 +799,8 @@
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="2:5" ht="62" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="11" t="s">
+    <row r="11" spans="2:5" ht="63.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -813,8 +813,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="2:5" ht="62" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B12" s="12"/>
+    <row r="12" spans="2:5" ht="63.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="6"/>
       <c r="C12" s="3" t="s">
         <v>6</v>
       </c>
@@ -825,8 +825,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="2:5" ht="41.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B13" s="11" t="s">
+    <row r="13" spans="2:5" ht="42.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -839,8 +839,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="62" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B14" s="12"/>
+    <row r="14" spans="2:5" ht="63.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="6"/>
       <c r="C14" s="3" t="s">
         <v>6</v>
       </c>
@@ -851,8 +851,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="2:5" ht="62" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B15" s="11" t="s">
+    <row r="15" spans="2:5" ht="63.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B15" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -865,34 +865,34 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="2:5" ht="103" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="13"/>
-      <c r="C16" s="14" t="s">
+    <row r="16" spans="2:5" ht="105.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="7"/>
+      <c r="C16" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E16" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="105.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="7"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="63.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="6"/>
+      <c r="C18" s="4" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" ht="103" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="13"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" ht="41.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="12"/>
-      <c r="C18" s="4" t="s">
-        <v>35</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
